--- a/Raw_Data/Wheat_Potato_av_losses.xlsx
+++ b/Raw_Data/Wheat_Potato_av_losses.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StefanÅström\C_Verktyg\Python\ALL_PYTHON\CBA_GOT_PROT\CBA_GBG_PROT\Raw_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StefanÅström\C_Verktyg\Python\ALL_PYTHON\2026_v7_Goth_Prot_CBA\Raw_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471112B4-6BE1-4EFB-82C0-E4ABF91D028D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D57060F-FC57-4908-A744-2D5F0FB1F0B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="43">
   <si>
     <t>Scenario_UKCEH</t>
   </si>
@@ -120,30 +120,6 @@
     <t>MTFR_v5a</t>
   </si>
   <si>
-    <t>A1r/d/D/v6b</t>
-  </si>
-  <si>
-    <t>C1/d/D/v6b</t>
-  </si>
-  <si>
-    <t>D1/d/D/v6b</t>
-  </si>
-  <si>
-    <t>C2/d/D/v6b</t>
-  </si>
-  <si>
-    <t>D2/d/D/v6b</t>
-  </si>
-  <si>
-    <t>D3/d/D/v6b</t>
-  </si>
-  <si>
-    <t>MTFR_v6b</t>
-  </si>
-  <si>
-    <t>Base_v6b</t>
-  </si>
-  <si>
     <t>Exceeded</t>
   </si>
   <si>
@@ -154,6 +130,42 @@
   </si>
   <si>
     <t>59.1813407998705319332491666158066275918</t>
+  </si>
+  <si>
+    <t>OPT Health -50 AAE -35 v7a</t>
+  </si>
+  <si>
+    <t>OPT Health -50 AAE -40 v7a</t>
+  </si>
+  <si>
+    <t>Baseline_v7a</t>
+  </si>
+  <si>
+    <t>OPT Health -50 AAE -45 v7a</t>
+  </si>
+  <si>
+    <t>OPT Health -50 AAE -50 v7a</t>
+  </si>
+  <si>
+    <t>OPT Health -55 AAE -40 v7a</t>
+  </si>
+  <si>
+    <t>OPT Health -55 AAE -45 v7a</t>
+  </si>
+  <si>
+    <t>OPT Health -55 AAE -50 v7a</t>
+  </si>
+  <si>
+    <t>OPT Health -60 AAE -40 v7a</t>
+  </si>
+  <si>
+    <t>OPT Health -60 AAE -45 v7a</t>
+  </si>
+  <si>
+    <t>OPT Health -60 AAE -50 v7a</t>
+  </si>
+  <si>
+    <t>MTFR_v7a</t>
   </si>
 </sst>
 </file>
@@ -530,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348CECE6-37D6-4610-9281-5AA8118B84FB}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="16.21875" customWidth="1"/>
@@ -912,7 +924,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C36" t="s">
         <v>6</v>
@@ -920,7 +932,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
         <v>6</v>
@@ -928,7 +940,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
         <v>6</v>
@@ -936,7 +948,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s">
         <v>6</v>
@@ -944,7 +956,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C40" t="s">
         <v>6</v>
@@ -952,7 +964,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C41" t="s">
         <v>6</v>
@@ -960,7 +972,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C42" t="s">
         <v>6</v>
@@ -968,7 +980,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C43" t="s">
         <v>6</v>
@@ -976,39 +988,39 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C48" t="s">
         <v>23</v>
@@ -1032,9 +1044,73 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C51" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C53" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>42</v>
+      </c>
+      <c r="C59" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1067,7 +1143,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1084,7 +1160,7 @@
         <v>3160000</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1101,7 +1177,7 @@
         <v>3520000</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1118,7 +1194,7 @@
         <v>3720000</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1149,7 +1225,7 @@
         <v>790000</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1166,7 +1242,7 @@
         <v>900000</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1183,7 +1259,7 @@
         <v>950000</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1206,65 +1282,22 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0">4FMPXW5WT43S-1005746519-433</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0">
+      <Url>https://anthesisllc.sharepoint.com/teams/External_-_Nordic_SLCPs_365/_layouts/15/DocIdRedir.aspx?ID=4FMPXW5WT43S-1005746519-433</Url>
+      <Description>4FMPXW5WT43S-1005746519-433</Description>
+    </_dlc_DocIdUrl>
+    <TaxCatchAll xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="458478d6-e45f-463e-b166-5a01b5e53481">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EE726821B4414D4F801789566814E9B0" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d7d3d3f934096697b26fe23ddd307665">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="64bc8f4d-cac8-469d-840e-d8b6f8e247f0" xmlns:ns3="458478d6-e45f-463e-b166-5a01b5e53481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7a52f90cd5745e772e9e0d9d94906982" ns2:_="" ns3:_="">
     <xsd:import namespace="64bc8f4d-cac8-469d-840e-d8b6f8e247f0"/>
@@ -1518,39 +1551,77 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0">4FMPXW5WT43S-1005746519-433</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0">
-      <Url>https://anthesisllc.sharepoint.com/teams/External_-_Nordic_SLCPs_365/_layouts/15/DocIdRedir.aspx?ID=4FMPXW5WT43S-1005746519-433</Url>
-      <Description>4FMPXW5WT43S-1005746519-433</Description>
-    </_dlc_DocIdUrl>
-    <TaxCatchAll xmlns="64bc8f4d-cac8-469d-840e-d8b6f8e247f0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="458478d6-e45f-463e-b166-5a01b5e53481">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28D88257-257C-4710-B412-AFFAC3F77BA1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{972C03D6-94A4-4AC4-AFF5-779D9FE59451}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="64bc8f4d-cac8-469d-840e-d8b6f8e247f0"/>
+    <ds:schemaRef ds:uri="458478d6-e45f-463e-b166-5a01b5e53481"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47D3A4AB-5A2F-4FE5-9322-F38EE22A076E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85B46724-5951-438B-9D46-2B31C5F3DC27}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1569,13 +1640,18 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47D3A4AB-5A2F-4FE5-9322-F38EE22A076E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{972C03D6-94A4-4AC4-AFF5-779D9FE59451}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28D88257-257C-4710-B412-AFFAC3F77BA1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="64bc8f4d-cac8-469d-840e-d8b6f8e247f0"/>
-    <ds:schemaRef ds:uri="458478d6-e45f-463e-b166-5a01b5e53481"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>